--- a/5. Other/Danh sách VNSH03 lô 500 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 500 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED418AA-D3D8-43FC-876E-92CE1B15061A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7868E56-F4F9-481A-BC2A-8BBF019DA529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="492">
   <si>
     <t>STT</t>
   </si>
@@ -1986,6 +1986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G471"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4016,7 +4017,7 @@
       <c r="E124" s="12"/>
       <c r="F124" s="12"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -6274,7 +6275,9 @@
       <c r="C265" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D265" s="4"/>
+      <c r="D265" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E265" s="4"/>
       <c r="F265" s="4"/>
     </row>
@@ -6320,7 +6323,9 @@
       <c r="C268" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D268" s="4"/>
+      <c r="D268" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E268" s="4"/>
       <c r="F268" s="4"/>
     </row>
@@ -6350,7 +6355,9 @@
       <c r="C270" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D270" s="4"/>
+      <c r="D270" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E270" s="4"/>
       <c r="F270" s="4"/>
     </row>
@@ -6364,7 +6371,9 @@
       <c r="C271" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D271" s="4"/>
+      <c r="D271" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E271" s="4"/>
       <c r="F271" s="4"/>
     </row>
@@ -6396,7 +6405,9 @@
       <c r="C273" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D273" s="4"/>
+      <c r="D273" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E273" s="4"/>
       <c r="F273" s="4"/>
     </row>
@@ -6410,7 +6421,9 @@
       <c r="C274" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D274" s="4"/>
+      <c r="D274" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E274" s="4"/>
       <c r="F274" s="4"/>
     </row>
@@ -6424,7 +6437,9 @@
       <c r="C275" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D275" s="4"/>
+      <c r="D275" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E275" s="4"/>
       <c r="F275" s="4"/>
     </row>
@@ -6438,7 +6453,9 @@
       <c r="C276" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D276" s="4"/>
+      <c r="D276" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E276" s="4"/>
       <c r="F276" s="4"/>
     </row>
@@ -6468,7 +6485,9 @@
       <c r="C278" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D278" s="4"/>
+      <c r="D278" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E278" s="4"/>
       <c r="F278" s="4"/>
     </row>
@@ -6482,7 +6501,9 @@
       <c r="C279" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D279" s="4"/>
+      <c r="D279" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E279" s="4"/>
       <c r="F279" s="4"/>
     </row>
@@ -6496,7 +6517,9 @@
       <c r="C280" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D280" s="4"/>
+      <c r="D280" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E280" s="4"/>
       <c r="F280" s="4"/>
     </row>
@@ -6542,7 +6565,9 @@
       <c r="C283" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D283" s="4"/>
+      <c r="D283" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E283" s="4"/>
       <c r="F283" s="4"/>
     </row>
@@ -6556,7 +6581,9 @@
       <c r="C284" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D284" s="4"/>
+      <c r="D284" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E284" s="4"/>
       <c r="F284" s="4"/>
     </row>
@@ -6570,7 +6597,9 @@
       <c r="C285" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D285" s="4"/>
+      <c r="D285" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E285" s="4"/>
       <c r="F285" s="4"/>
     </row>
@@ -6584,7 +6613,9 @@
       <c r="C286" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D286" s="4"/>
+      <c r="D286" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E286" s="4"/>
       <c r="F286" s="4"/>
     </row>
@@ -6598,7 +6629,9 @@
       <c r="C287" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D287" s="4"/>
+      <c r="D287" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E287" s="4"/>
       <c r="F287" s="4"/>
     </row>
@@ -6612,7 +6645,9 @@
       <c r="C288" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D288" s="4"/>
+      <c r="D288" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E288" s="4"/>
       <c r="F288" s="4"/>
     </row>
@@ -6626,7 +6661,9 @@
       <c r="C289" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D289" s="4"/>
+      <c r="D289" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E289" s="4"/>
       <c r="F289" s="4"/>
     </row>
@@ -6656,7 +6693,9 @@
       <c r="C291" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D291" s="4"/>
+      <c r="D291" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E291" s="4"/>
       <c r="F291" s="4"/>
     </row>
@@ -6670,7 +6709,9 @@
       <c r="C292" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D292" s="4"/>
+      <c r="D292" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E292" s="4"/>
       <c r="F292" s="4"/>
     </row>
@@ -6684,7 +6725,9 @@
       <c r="C293" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D293" s="4"/>
+      <c r="D293" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E293" s="4"/>
       <c r="F293" s="4"/>
     </row>
@@ -6698,7 +6741,9 @@
       <c r="C294" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D294" s="4"/>
+      <c r="D294" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E294" s="4"/>
       <c r="F294" s="4"/>
     </row>
@@ -6728,7 +6773,9 @@
       <c r="C296" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D296" s="4"/>
+      <c r="D296" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E296" s="4"/>
       <c r="F296" s="4"/>
     </row>
@@ -6742,7 +6789,9 @@
       <c r="C297" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D297" s="4"/>
+      <c r="D297" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E297" s="4"/>
       <c r="F297" s="4"/>
     </row>
@@ -6788,7 +6837,9 @@
       <c r="C300" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D300" s="4"/>
+      <c r="D300" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E300" s="4"/>
       <c r="F300" s="4"/>
     </row>
@@ -6802,7 +6853,9 @@
       <c r="C301" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D301" s="4"/>
+      <c r="D301" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E301" s="4"/>
       <c r="F301" s="4"/>
     </row>
@@ -6912,7 +6965,9 @@
       <c r="C308" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D308" s="4"/>
+      <c r="D308" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E308" s="4"/>
       <c r="F308" s="4"/>
     </row>
@@ -6990,7 +7045,9 @@
       <c r="C313" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D313" s="4"/>
+      <c r="D313" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E313" s="4"/>
       <c r="F313" s="4"/>
     </row>
@@ -7068,7 +7125,9 @@
       <c r="C318" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D318" s="4"/>
+      <c r="D318" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E318" s="4"/>
       <c r="F318" s="4"/>
     </row>
@@ -7098,7 +7157,9 @@
       <c r="C320" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D320" s="4"/>
+      <c r="D320" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E320" s="4"/>
       <c r="F320" s="4"/>
     </row>
@@ -7192,7 +7253,9 @@
       <c r="C326" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D326" s="4"/>
+      <c r="D326" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E326" s="4"/>
       <c r="F326" s="4"/>
     </row>
@@ -7206,7 +7269,9 @@
       <c r="C327" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D327" s="4"/>
+      <c r="D327" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E327" s="4"/>
       <c r="F327" s="4"/>
     </row>
@@ -7252,7 +7317,9 @@
       <c r="C330" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D330" s="4"/>
+      <c r="D330" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E330" s="4"/>
       <c r="F330" s="4"/>
     </row>
@@ -7266,7 +7333,9 @@
       <c r="C331" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D331" s="4"/>
+      <c r="D331" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E331" s="4"/>
       <c r="F331" s="4"/>
     </row>
@@ -7280,7 +7349,9 @@
       <c r="C332" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D332" s="4"/>
+      <c r="D332" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E332" s="4"/>
       <c r="F332" s="4"/>
     </row>
@@ -7310,7 +7381,9 @@
       <c r="C334" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D334" s="4"/>
+      <c r="D334" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E334" s="4"/>
       <c r="F334" s="4"/>
     </row>
@@ -7324,7 +7397,9 @@
       <c r="C335" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D335" s="4"/>
+      <c r="D335" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E335" s="4"/>
       <c r="F335" s="4"/>
     </row>
@@ -7418,7 +7493,9 @@
       <c r="C341" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D341" s="4"/>
+      <c r="D341" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E341" s="4"/>
       <c r="F341" s="4"/>
     </row>
@@ -7432,7 +7509,9 @@
       <c r="C342" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D342" s="4"/>
+      <c r="D342" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E342" s="4"/>
       <c r="F342" s="4"/>
     </row>
@@ -7510,7 +7589,9 @@
       <c r="C347" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D347" s="4"/>
+      <c r="D347" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E347" s="4"/>
       <c r="F347" s="4"/>
     </row>
@@ -7572,7 +7653,9 @@
       <c r="C351" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D351" s="4"/>
+      <c r="D351" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E351" s="4"/>
       <c r="F351" s="4"/>
     </row>
@@ -7586,7 +7669,9 @@
       <c r="C352" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D352" s="4"/>
+      <c r="D352" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E352" s="4"/>
       <c r="F352" s="4"/>
     </row>
@@ -9513,7 +9598,13 @@
       <c r="F471" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E471" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
+  <autoFilter ref="A1:E471" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Đã nhập kho"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
